--- a/Protothreads/b_Blinky_and_Serial/measured_data.xlsx
+++ b/Protothreads/b_Blinky_and_Serial/measured_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thomas\Documents\Courses\ECE5995\eye-tracking-project\Protothreads\b_Blinky_and_Serial\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51EAE1EA-C7AF-4ABE-A27A-859FDFE96203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90816A4E-F42B-4D7E-9EBF-1E9946AA742F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="16">
   <si>
     <t>Actual angle</t>
   </si>
@@ -80,6 +80,9 @@
   </si>
   <si>
     <t>337.5 (157.5)</t>
+  </si>
+  <si>
+    <t>ground-truth angle</t>
   </si>
 </sst>
 </file>
@@ -191,7 +194,7 @@
             </a:r>
             <a:r>
               <a:rPr lang="en-US" baseline="0"/>
-              <a:t> 3-Axis Linear Sensor</a:t>
+              <a:t> 3-Axis Hall-Effect Linear Sensor</a:t>
             </a:r>
             <a:endParaRPr lang="en-US"/>
           </a:p>
@@ -241,7 +244,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>actual angle</c:v>
+                  <c:v>ground-truth angle</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -847,7 +850,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>actual angle</c:v>
+                  <c:v>ground-truth angle</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3668,7 +3671,7 @@
     </row>
     <row r="25" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>3</v>
@@ -3677,7 +3680,7 @@
         <v>4</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>3</v>
